--- a/ZonasEscolares/excels/LIMA-LIMA-RIMAC.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-RIMAC.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-RIMAC.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-RIMAC.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>049 NUESTRA SEÑORA DE GUADALUPE</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.03037</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-77.03149999999999</v>
-      </c>
-      <c r="I2" t="n">
-        <v>359</v>
-      </c>
-      <c r="J2" t="n">
-        <v>20</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.03037</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-77.0315</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>0320</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.016013</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-77.030832</v>
-      </c>
-      <c r="I3" t="n">
-        <v>250</v>
-      </c>
-      <c r="J3" t="n">
-        <v>13</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.016013</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-77.030832</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>0391-2 SAN JUAN DE AMANCAES</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.016</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-77.02679999999999</v>
-      </c>
-      <c r="I4" t="n">
-        <v>312</v>
-      </c>
-      <c r="J4" t="n">
-        <v>21</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.016</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-77.0268</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>0392-3 SAN CRISTOBAL / 3003 SAN CRISTOBAL</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.03695</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-77.02269</v>
-      </c>
-      <c r="I5" t="n">
-        <v>695</v>
-      </c>
-      <c r="J5" t="n">
-        <v>36</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.03695</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-77.02269</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>RICARDO BENTIN</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.0304</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-77.03694</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2719</v>
-      </c>
-      <c r="J6" t="n">
-        <v>176</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.0304</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-77.03694</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>NACIONAL RIMAC</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.01898</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-77.03552000000001</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1091</v>
-      </c>
-      <c r="J7" t="n">
-        <v>51</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.01898</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-77.03552</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1091</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>2002 MARISCAL RAMON CASTILLA</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.01641</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-77.03184</v>
-      </c>
-      <c r="I8" t="n">
-        <v>552</v>
-      </c>
-      <c r="J8" t="n">
-        <v>28</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.01641</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-77.03184</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>2004</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.03823</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-77.01868</v>
-      </c>
-      <c r="I9" t="n">
-        <v>204</v>
-      </c>
-      <c r="J9" t="n">
-        <v>11</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.03823</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-77.01868</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>2063 CORONEL JOSE FELIX BOGADO</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-12.01485</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-77.02612000000001</v>
-      </c>
-      <c r="I10" t="n">
-        <v>964</v>
-      </c>
-      <c r="J10" t="n">
-        <v>46</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.01485</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-77.02612</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>964</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>2074 MARIA PARADO DE BELLIDO</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-12.029525</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-77.028075</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2080</v>
-      </c>
-      <c r="J11" t="n">
-        <v>105</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-12.029525</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-77.028075</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>2083 VIRGEN DEL CARMEN</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-12.0307</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-77.03149999999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1109</v>
-      </c>
-      <c r="J12" t="n">
-        <v>43</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-12.0307</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-77.0315</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1109</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>3001 ESTADOS UNIDOS MEXICANOS</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.03949</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-77.02807</v>
-      </c>
-      <c r="I13" t="n">
-        <v>384</v>
-      </c>
-      <c r="J13" t="n">
-        <v>18</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.03949</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-77.02807</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>3004 ESPAÑA</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-12.0367</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-77.02679999999999</v>
-      </c>
-      <c r="I14" t="n">
-        <v>606</v>
-      </c>
-      <c r="J14" t="n">
-        <v>32</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-12.0367</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-77.0268</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>3006 JOSE ERNESTO ECHENIQUE RODRIGUEZ</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.03736</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-77.015</v>
-      </c>
-      <c r="I15" t="n">
-        <v>397</v>
-      </c>
-      <c r="J15" t="n">
-        <v>22</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.03736</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-77.015</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>3010 RAMON CASTILLA</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.03648</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-77.03897000000001</v>
-      </c>
-      <c r="I16" t="n">
-        <v>478</v>
-      </c>
-      <c r="J16" t="n">
-        <v>29</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.03648</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-77.03897</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>3012 JESUS DIVINO MAESTRO</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-12.02158</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-77.02685</v>
-      </c>
-      <c r="I17" t="n">
-        <v>338</v>
-      </c>
-      <c r="J17" t="n">
-        <v>16</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-12.02158</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-77.02685</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>3015 LOS ANGELES DE JESUS</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-12.023383</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-77.026933</v>
-      </c>
-      <c r="I18" t="n">
-        <v>884</v>
-      </c>
-      <c r="J18" t="n">
-        <v>41</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-12.023383</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-77.026933</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>884</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>3017 INMACULADA CONCEPCION</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-12.01641</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-77.03202</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1032</v>
-      </c>
-      <c r="J19" t="n">
-        <v>45</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-12.01641</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-77.03202</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1032</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>3019 PATRICIA TERESA RODRIGUEZ</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-12.02403</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-77.02494</v>
-      </c>
-      <c r="I20" t="n">
-        <v>354</v>
-      </c>
-      <c r="J20" t="n">
-        <v>22</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-12.02403</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-77.02494</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>3021 SAN JUAN MACIAS</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-12.0392</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-77.029</v>
-      </c>
-      <c r="I21" t="n">
-        <v>548</v>
-      </c>
-      <c r="J21" t="n">
-        <v>27</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-12.0392</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-77.029</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>LUCIE RYNNING DE ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-12.0356</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-77.0264</v>
-      </c>
-      <c r="I22" t="n">
-        <v>480</v>
-      </c>
-      <c r="J22" t="n">
-        <v>33</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-12.0356</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-77.0264</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>CARLOS PAREJA PAZ SOLDAN</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-12.03636</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-77.02361999999999</v>
-      </c>
-      <c r="I23" t="n">
-        <v>331</v>
-      </c>
-      <c r="J23" t="n">
-        <v>26</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-12.03636</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-77.02362</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>ESTHER CACERES SALGADO</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-12.03029</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-77.03107</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1007</v>
-      </c>
-      <c r="J24" t="n">
-        <v>58</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-12.03029</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-77.03107</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>DORA MAYER DE ZULEN</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-12.02727</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-77.03435</v>
-      </c>
-      <c r="I25" t="n">
-        <v>227</v>
-      </c>
-      <c r="J25" t="n">
-        <v>19</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-12.02727</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-77.03435</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>NUESTRA SEÑORA DE LA CONSOLACION</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-12.026783</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-77.031533</v>
-      </c>
-      <c r="I26" t="n">
-        <v>511</v>
-      </c>
-      <c r="J26" t="n">
-        <v>51</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-12.026783</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-77.031533</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>REINO DEL SABER SCHOOL</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-12.02641</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-77.03309</v>
-      </c>
-      <c r="I27" t="n">
-        <v>9</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-12.02641</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-77.03309</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>CESAR VALLEJO</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-12.01822</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-77.02813</v>
-      </c>
-      <c r="I28" t="n">
-        <v>434</v>
-      </c>
-      <c r="J28" t="n">
-        <v>28</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-12.01822</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-77.02813</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>SANTA CECILIA</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-12.034</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-77.02518000000001</v>
-      </c>
-      <c r="I29" t="n">
-        <v>189</v>
-      </c>
-      <c r="J29" t="n">
-        <v>20</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-12.034</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-77.02518</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>BAUTISTA</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-12.021983</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-77.030867</v>
-      </c>
-      <c r="I30" t="n">
-        <v>219</v>
-      </c>
-      <c r="J30" t="n">
-        <v>39</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-12.021983</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-77.030867</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>LOS SIERVOS DE JESUS</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-12.0196</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-77.02930000000001</v>
-      </c>
-      <c r="I31" t="n">
-        <v>201</v>
-      </c>
-      <c r="J31" t="n">
-        <v>16</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-12.0196</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-77.0293</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>INSTITUTO SEVILLA</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-12.03635</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-77.02566</v>
-      </c>
-      <c r="I32" t="n">
-        <v>421</v>
-      </c>
-      <c r="J32" t="n">
-        <v>29</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-12.03635</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-77.02566</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>NUESTRA SEÑORA DEL PATROCINIO</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-12.0364</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-77.024733</v>
-      </c>
-      <c r="I33" t="n">
-        <v>245</v>
-      </c>
-      <c r="J33" t="n">
-        <v>27</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-12.0364</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-77.024733</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>NUESTRA SEÑORA DE LOS ANGELES</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-12.0357</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-77.02549999999999</v>
-      </c>
-      <c r="I34" t="n">
-        <v>244</v>
-      </c>
-      <c r="J34" t="n">
-        <v>12</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-12.0357</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-77.0255</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>JUAN JACOBO ROUSSEAU</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-12.0252</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-77.03622</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-12.0252</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-77.03622</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>SANTA RITA DE CASIA</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-12.03833</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-77.02741</v>
-      </c>
-      <c r="I36" t="n">
-        <v>169</v>
-      </c>
-      <c r="J36" t="n">
-        <v>16</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-12.03833</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-77.02741</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>ESTRELLITA DE LUZ</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-12.03827</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-77.01609000000001</v>
-      </c>
-      <c r="I37" t="n">
-        <v>13</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2</v>
-      </c>
-      <c r="K37" t="n">
-        <v>1</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-12.03827</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-77.01609</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>COMUNIDAD SHIPIBA</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-12.04218</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-77.01759</v>
-      </c>
-      <c r="I38" t="n">
-        <v>246</v>
-      </c>
-      <c r="J38" t="n">
-        <v>12</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-12.04218</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-77.01759</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>NUESTRA SEÑORA DE LAS MERCEDES DEL BOSQUE</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-12.025821</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-77.031486</v>
-      </c>
-      <c r="I39" t="n">
-        <v>252</v>
-      </c>
-      <c r="J39" t="n">
-        <v>4</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-12.025821</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-77.031486</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>JESUS EL NAZARENO</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-12.0246</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-77.03158000000001</v>
-      </c>
-      <c r="I40" t="n">
-        <v>233</v>
-      </c>
-      <c r="J40" t="n">
-        <v>14</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-12.0246</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-77.03158</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>COLEGIO MONSERRAT DEL RIMAC</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-12.02541</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-77.03440999999999</v>
-      </c>
-      <c r="I41" t="n">
-        <v>226</v>
-      </c>
-      <c r="J41" t="n">
-        <v>18</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-12.02541</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-77.03441</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>VIRGEN NIÑA</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-12.0239</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-77.02849999999999</v>
-      </c>
-      <c r="I42" t="n">
-        <v>300</v>
-      </c>
-      <c r="J42" t="n">
-        <v>20</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-12.0239</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-77.0285</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>NUESTRA SEÑORA DE LAS MERCEDES DEL BOSQUE</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-12.02053</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-77.03187</v>
-      </c>
-      <c r="I43" t="n">
-        <v>293</v>
-      </c>
-      <c r="J43" t="n">
-        <v>26</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-12.02053</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-77.03187</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>EMANUEL &amp; DEZA SCHOOL- KENZIT</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-12.0271</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-77.0287</v>
-      </c>
-      <c r="I44" t="n">
-        <v>446</v>
-      </c>
-      <c r="J44" t="n">
-        <v>14</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-12.0271</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-77.0287</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>ANCILA DEI</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-12.03135</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-77.02513</v>
-      </c>
-      <c r="I45" t="n">
-        <v>123</v>
-      </c>
-      <c r="J45" t="n">
-        <v>12</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-12.03135</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-77.02513</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>NIÑO REY DE PIEDRA LIZA / NIÑO REY DE PIEDRA LIZA I</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-12.03916</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-77.01721000000001</v>
-      </c>
-      <c r="I46" t="n">
-        <v>100</v>
-      </c>
-      <c r="J46" t="n">
-        <v>10</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-12.03916</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-77.01721</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>NUESTRA SEÑORA DEL ROSARIO DEL RIMAC</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-12.02619</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-77.03658</v>
-      </c>
-      <c r="I47" t="n">
-        <v>460</v>
-      </c>
-      <c r="J47" t="n">
-        <v>21</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-12.02619</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-77.03658</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>INNOVA SCHOOLS - RIMAC SPORTING CRISTAL</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-12.01977</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-77.03457</v>
-      </c>
-      <c r="I48" t="n">
-        <v>1130</v>
-      </c>
-      <c r="J48" t="n">
-        <v>38</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-12.01977</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-77.03457</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>FAMILIA UNIVERSAL SCHOOL</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-12.02645</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-77.02818000000001</v>
-      </c>
-      <c r="I49" t="n">
-        <v>540</v>
-      </c>
-      <c r="J49" t="n">
-        <v>22</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-12.02645</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-77.02818</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>SAN JUAN BAUTISTA - RIMAC</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-12.02184</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-77.03097</v>
-      </c>
-      <c r="I50" t="n">
-        <v>203</v>
-      </c>
-      <c r="J50" t="n">
-        <v>14</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-12.02184</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-77.03097</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LIMA-LIMA-RIMAC.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-RIMAC.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>320488</t>
+          <t>321529</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>049 NUESTRA SEÑORA DE GUADALUPE</t>
+          <t>JUAN JACOBO ROUSSEAU</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.03037</t>
+          <t>-12.0252</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.0315</t>
+          <t>-77.03622</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>320501</t>
+          <t>321001</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0320</t>
+          <t>REINO DEL SABER SCHOOL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.016013</t>
+          <t>-12.02641</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.030832</t>
+          <t>-77.03309</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>320558</t>
+          <t>696453</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0391-2 SAN JUAN DE AMANCAES</t>
+          <t>NIÑO REY DE PIEDRA LIZA / NIÑO REY DE PIEDRA LIZA I</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.016</t>
+          <t>-12.03916</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.0268</t>
+          <t>-77.01721</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>320582</t>
+          <t>320662</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0392-3 SAN CRISTOBAL / 3003 SAN CRISTOBAL</t>
+          <t>2074 MARIA PARADO DE BELLIDO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.03695</t>
+          <t>-12.029525</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.02269</t>
+          <t>-77.028075</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>105</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>320619</t>
+          <t>320643</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RICARDO BENTIN</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.0304</t>
+          <t>-12.03823</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.03694</t>
+          <t>-77.01868</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>204</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>320624</t>
+          <t>321464</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NACIONAL RIMAC</t>
+          <t>NUESTRA SEÑORA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.01898</t>
+          <t>-12.0357</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.03552</t>
+          <t>-77.0255</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>244</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>320638</t>
+          <t>529398</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2002 MARISCAL RAMON CASTILLA</t>
+          <t>COMUNIDAD SHIPIBA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.01641</t>
+          <t>-12.04218</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.03184</t>
+          <t>-77.01759</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>246</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>320643</t>
+          <t>696250</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>ANCILA DEI</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.03823</t>
+          <t>-12.03135</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.01868</t>
+          <t>-77.02513</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>123</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>320657</t>
+          <t>320501</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2063 CORONEL JOSE FELIX BOGADO</t>
+          <t>0320</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.01485</t>
+          <t>-12.016013</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.02612</t>
+          <t>-77.030832</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>320662</t>
+          <t>590135</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2074 MARIA PARADO DE BELLIDO</t>
+          <t>JESUS EL NAZARENO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.029525</t>
+          <t>-12.0246</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.028075</t>
+          <t>-77.03158</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>233</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>320676</t>
+          <t>695967</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2083 VIRGEN DEL CARMEN</t>
+          <t>EMANUEL &amp; DEZA SCHOOL- KENZIT</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.0307</t>
+          <t>-12.0271</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.0315</t>
+          <t>-77.0287</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>446</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>320681</t>
+          <t>848593</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3001 ESTADOS UNIDOS MEXICANOS</t>
+          <t>SAN JUAN BAUTISTA - RIMAC</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.03949</t>
+          <t>-12.02184</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.02807</t>
+          <t>-77.03097</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>203</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>320704</t>
+          <t>320761</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>3004 ESPAÑA</t>
+          <t>3012 JESUS DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.0367</t>
+          <t>-12.02158</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.0268</t>
+          <t>-77.02685</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>338</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>320723</t>
+          <t>321355</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>3006 JOSE ERNESTO ECHENIQUE RODRIGUEZ</t>
+          <t>LOS SIERVOS DE JESUS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.03736</t>
+          <t>-12.0196</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.015</t>
+          <t>-77.0293</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>201</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1369,37 +1369,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>320756</t>
+          <t>321609</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>3010 RAMON CASTILLA</t>
+          <t>SANTA RITA DE CASIA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.03648</t>
+          <t>-12.03833</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.03897</t>
+          <t>-77.02741</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>169</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>320761</t>
+          <t>320619</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>3012 JESUS DIVINO MAESTRO</t>
+          <t>RICARDO BENTIN</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.02158</t>
+          <t>-12.0304</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.02685</t>
+          <t>-77.03694</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>176</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>320780</t>
+          <t>320681</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>3015 LOS ANGELES DE JESUS</t>
+          <t>3001 ESTADOS UNIDOS MEXICANOS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.023383</t>
+          <t>-12.03949</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.026933</t>
+          <t>-77.02807</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>384</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>320799</t>
+          <t>694576</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3017 INMACULADA CONCEPCION</t>
+          <t>COLEGIO MONSERRAT DEL RIMAC</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.01641</t>
+          <t>-12.02541</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.03202</t>
+          <t>-77.03441</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>226</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>320817</t>
+          <t>320916</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>3019 PATRICIA TERESA RODRIGUEZ</t>
+          <t>DORA MAYER DE ZULEN</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.02403</t>
+          <t>-12.02727</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.02494</t>
+          <t>-77.03435</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>227</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1679,37 +1679,37 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>320822</t>
+          <t>321647</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>3021 SAN JUAN MACIAS</t>
+          <t>ESTRELLITA DE LUZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.0392</t>
+          <t>-12.03827</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.029</t>
+          <t>-77.01609</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>320841</t>
+          <t>320488</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>LUCIE RYNNING DE ANTUNEZ DE MAYOLO</t>
+          <t>049 NUESTRA SEÑORA DE GUADALUPE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.0356</t>
+          <t>-12.03037</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.0264</t>
+          <t>-77.0315</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>359</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1803,37 +1803,37 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>320860</t>
+          <t>321100</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CARLOS PAREJA PAZ SOLDAN</t>
+          <t>SANTA CECILIA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.03636</t>
+          <t>-12.034</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-77.02362</t>
+          <t>-77.02518</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>189</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>320879</t>
+          <t>694977</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ESTHER CACERES SALGADO</t>
+          <t>VIRGEN NIÑA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.03029</t>
+          <t>-12.0239</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.03107</t>
+          <t>-77.0285</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>320916</t>
+          <t>320558</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>DORA MAYER DE ZULEN</t>
+          <t>0391-2 SAN JUAN DE AMANCAES</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.02727</t>
+          <t>-12.016</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.03435</t>
+          <t>-77.0268</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>312</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>320935</t>
+          <t>698386</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA CONSOLACION</t>
+          <t>NUESTRA SEÑORA DEL ROSARIO DEL RIMAC</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.026783</t>
+          <t>-12.02619</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-77.031533</t>
+          <t>-77.03658</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>460</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2051,37 +2051,37 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>321001</t>
+          <t>320723</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>REINO DEL SABER SCHOOL</t>
+          <t>3006 JOSE ERNESTO ECHENIQUE RODRIGUEZ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.02641</t>
+          <t>-12.03736</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.03309</t>
+          <t>-77.015</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>397</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>321063</t>
+          <t>320817</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO</t>
+          <t>3019 PATRICIA TERESA RODRIGUEZ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.01822</t>
+          <t>-12.02403</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.02813</t>
+          <t>-77.02494</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>354</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2175,37 +2175,37 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>321100</t>
+          <t>729076</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SANTA CECILIA</t>
+          <t>FAMILIA UNIVERSAL SCHOOL</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.034</t>
+          <t>-12.02645</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.02518</t>
+          <t>-77.02818</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>540</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>321119</t>
+          <t>320860</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>BAUTISTA</t>
+          <t>CARLOS PAREJA PAZ SOLDAN</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.021983</t>
+          <t>-12.03636</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.030867</t>
+          <t>-77.02362</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>331</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>321355</t>
+          <t>695043</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>LOS SIERVOS DE JESUS</t>
+          <t>NUESTRA SEÑORA DE LAS MERCEDES DEL BOSQUE</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.0196</t>
+          <t>-12.02053</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-77.0293</t>
+          <t>-77.03187</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>293</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>321416</t>
+          <t>320822</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>INSTITUTO SEVILLA</t>
+          <t>3021 SAN JUAN MACIAS</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.03635</t>
+          <t>-12.0392</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-77.02566</t>
+          <t>-77.029</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>548</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>321464</t>
+          <t>320638</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LOS ANGELES</t>
+          <t>2002 MARISCAL RAMON CASTILLA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.0357</t>
+          <t>-12.01641</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-77.0255</t>
+          <t>-77.03184</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>552</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,37 +2547,37 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>321529</t>
+          <t>321063</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>JUAN JACOBO ROUSSEAU</t>
+          <t>CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.0252</t>
+          <t>-12.01822</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-77.03622</t>
+          <t>-77.02813</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>434</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2609,37 +2609,37 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>321609</t>
+          <t>320756</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SANTA RITA DE CASIA</t>
+          <t>3010 RAMON CASTILLA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.03833</t>
+          <t>-12.03648</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-77.02741</t>
+          <t>-77.03897</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>478</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2671,37 +2671,37 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>321647</t>
+          <t>321416</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ESTRELLITA DE LUZ</t>
+          <t>INSTITUTO SEVILLA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.03827</t>
+          <t>-12.03635</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-77.01609</t>
+          <t>-77.02566</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>421</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>529398</t>
+          <t>320704</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>COMUNIDAD SHIPIBA</t>
+          <t>3004 ESPAÑA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.04218</t>
+          <t>-12.0367</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-77.01759</t>
+          <t>-77.0268</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>606</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>533178</t>
+          <t>320841</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LAS MERCEDES DEL BOSQUE</t>
+          <t>LUCIE RYNNING DE ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.025821</t>
+          <t>-12.0356</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-77.031486</t>
+          <t>-77.0264</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>480</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>590135</t>
+          <t>320582</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>JESUS EL NAZARENO</t>
+          <t>0392-3 SAN CRISTOBAL / 3003 SAN CRISTOBAL</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.0246</t>
+          <t>-12.03695</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-77.03158</t>
+          <t>-77.02269</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>695</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>694576</t>
+          <t>717078</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>COLEGIO MONSERRAT DEL RIMAC</t>
+          <t>INNOVA SCHOOLS - RIMAC SPORTING CRISTAL</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.02541</t>
+          <t>-12.01977</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-77.03441</t>
+          <t>-77.03457</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>694977</t>
+          <t>321119</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>VIRGEN NIÑA</t>
+          <t>BAUTISTA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.0239</t>
+          <t>-12.021983</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-77.0285</t>
+          <t>-77.030867</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>219</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>695043</t>
+          <t>533178</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3053,22 +3053,22 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.02053</t>
+          <t>-12.025821</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-77.03187</t>
+          <t>-77.031486</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>252</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>695967</t>
+          <t>320780</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>EMANUEL &amp; DEZA SCHOOL- KENZIT</t>
+          <t>3015 LOS ANGELES DE JESUS</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.0271</t>
+          <t>-12.023383</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-77.0287</t>
+          <t>-77.026933</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>884</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>696250</t>
+          <t>320676</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ANCILA DEI</t>
+          <t>2083 VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-12.03135</t>
+          <t>-12.0307</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-77.02513</t>
+          <t>-77.0315</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,37 +3229,37 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>696453</t>
+          <t>320799</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>NIÑO REY DE PIEDRA LIZA / NIÑO REY DE PIEDRA LIZA I</t>
+          <t>3017 INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.03916</t>
+          <t>-12.01641</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-77.01721</t>
+          <t>-77.03202</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>698386</t>
+          <t>320657</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL ROSARIO DEL RIMAC</t>
+          <t>2063 CORONEL JOSE FELIX BOGADO</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-12.02619</t>
+          <t>-12.01485</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-77.03658</t>
+          <t>-77.02612</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>964</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>717078</t>
+          <t>320624</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - RIMAC SPORTING CRISTAL</t>
+          <t>NACIONAL RIMAC</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-12.01977</t>
+          <t>-12.01898</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-77.03457</t>
+          <t>-77.03552</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>729076</t>
+          <t>320935</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FAMILIA UNIVERSAL SCHOOL</t>
+          <t>NUESTRA SEÑORA DE LA CONSOLACION</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.02645</t>
+          <t>-12.026783</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-77.02818</t>
+          <t>-77.031533</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>511</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>848593</t>
+          <t>320879</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SAN JUAN BAUTISTA - RIMAC</t>
+          <t>ESTHER CACERES SALGADO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12.02184</t>
+          <t>-12.03029</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-77.03097</t>
+          <t>-77.03107</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-RIMAC.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-RIMAC.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>321529</t>
+          <t>848593</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>JUAN JACOBO ROUSSEAU</t>
+          <t>SAN JUAN BAUTISTA - RIMAC</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.0252</t>
+          <t>203</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.03622</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.02184</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-77.03097</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,42 +563,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>321001</t>
+          <t>729076</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>REINO DEL SABER SCHOOL</t>
+          <t>FAMILIA UNIVERSAL SCHOOL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.02641</t>
+          <t>540</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.03309</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-12.02645</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-77.02818</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -625,42 +625,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>696453</t>
+          <t>717078</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NIÑO REY DE PIEDRA LIZA / NIÑO REY DE PIEDRA LIZA I</t>
+          <t>INNOVA SCHOOLS - RIMAC SPORTING CRISTAL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.03916</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.01721</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>-12.01977</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.03457</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>320662</t>
+          <t>698386</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2074 MARIA PARADO DE BELLIDO</t>
+          <t>NUESTRA SEÑORA DEL ROSARIO DEL RIMAC</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.029525</t>
+          <t>460</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.028075</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>-12.02619</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>-77.03658</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,37 +749,37 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>320643</t>
+          <t>696453</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>NIÑO REY DE PIEDRA LIZA / NIÑO REY DE PIEDRA LIZA I</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.03823</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.01868</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>-12.03916</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.01721</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>321464</t>
+          <t>696250</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LOS ANGELES</t>
+          <t>ANCILA DEI</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.0357</t>
+          <t>123</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.0255</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>-12.03135</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.02513</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>529398</t>
+          <t>695967</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>COMUNIDAD SHIPIBA</t>
+          <t>EMANUEL &amp; DEZA SCHOOL- KENZIT</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.04218</t>
+          <t>446</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.01759</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>-12.0271</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.0287</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>696250</t>
+          <t>695043</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ANCILA DEI</t>
+          <t>NUESTRA SEÑORA DE LAS MERCEDES DEL BOSQUE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.03135</t>
+          <t>293</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.02513</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>-12.02053</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.03187</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>320501</t>
+          <t>694977</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0320</t>
+          <t>VIRGEN NIÑA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.016013</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.030832</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>-12.0239</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.0285</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>590135</t>
+          <t>694576</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JESUS EL NAZARENO</t>
+          <t>COLEGIO MONSERRAT DEL RIMAC</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.0246</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.03158</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>-12.02541</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.03441</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>695967</t>
+          <t>590135</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>EMANUEL &amp; DEZA SCHOOL- KENZIT</t>
+          <t>JESUS EL NAZARENO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.0271</t>
+          <t>233</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.0287</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>-12.0246</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.03158</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>848593</t>
+          <t>533178</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SAN JUAN BAUTISTA - RIMAC</t>
+          <t>NUESTRA SEÑORA DE LAS MERCEDES DEL BOSQUE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.02184</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.03097</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>-12.025821</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.031486</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>320761</t>
+          <t>529398</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>3012 JESUS DIVINO MAESTRO</t>
+          <t>COMUNIDAD SHIPIBA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.02158</t>
+          <t>246</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.02685</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>-12.04218</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.01759</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,42 +1307,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>321355</t>
+          <t>321647</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>LOS SIERVOS DE JESUS</t>
+          <t>ESTRELLITA DE LUZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.0196</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.0293</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>-12.03827</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.01609</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1379,22 +1379,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>-12.03833</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>-77.02741</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,37 +1431,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>320619</t>
+          <t>321529</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RICARDO BENTIN</t>
+          <t>JUAN JACOBO ROUSSEAU</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.0304</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.03694</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>-12.0252</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>-77.03622</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>320681</t>
+          <t>321464</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>3001 ESTADOS UNIDOS MEXICANOS</t>
+          <t>NUESTRA SEÑORA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.03949</t>
+          <t>244</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.02807</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>-12.0357</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.0255</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>694576</t>
+          <t>321459</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>COLEGIO MONSERRAT DEL RIMAC</t>
+          <t>NUESTRA SEÑORA DEL PATROCINIO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.02541</t>
+          <t>245</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.03441</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>-12.0364</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.024733</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>320916</t>
+          <t>321416</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>DORA MAYER DE ZULEN</t>
+          <t>INSTITUTO SEVILLA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.02727</t>
+          <t>421</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.03435</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>-12.03635</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.02566</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,42 +1679,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>321647</t>
+          <t>321355</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ESTRELLITA DE LUZ</t>
+          <t>LOS SIERVOS DE JESUS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.03827</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.01609</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-12.0196</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-77.0293</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>320488</t>
+          <t>321119</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>049 NUESTRA SEÑORA DE GUADALUPE</t>
+          <t>BAUTISTA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.03037</t>
+          <t>219</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.0315</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>-12.021983</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.030867</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1813,22 +1813,22 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>-12.034</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>-77.02518</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>694977</t>
+          <t>321063</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>VIRGEN NIÑA</t>
+          <t>CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.0239</t>
+          <t>434</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.0285</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>-12.01822</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.02813</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,37 +1927,37 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>320558</t>
+          <t>321001</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0391-2 SAN JUAN DE AMANCAES</t>
+          <t>REINO DEL SABER SCHOOL</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.016</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.0268</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>-12.02641</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.03309</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>698386</t>
+          <t>320935</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL ROSARIO DEL RIMAC</t>
+          <t>NUESTRA SEÑORA DE LA CONSOLACION</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.02619</t>
+          <t>511</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-77.03658</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>-12.026783</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.031533</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>320723</t>
+          <t>320916</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>3006 JOSE ERNESTO ECHENIQUE RODRIGUEZ</t>
+          <t>DORA MAYER DE ZULEN</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.03736</t>
+          <t>227</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.015</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>-12.02727</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.03435</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>320817</t>
+          <t>320879</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>3019 PATRICIA TERESA RODRIGUEZ</t>
+          <t>ESTHER CACERES SALGADO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.02403</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.02494</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>-12.03029</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.03107</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>729076</t>
+          <t>320860</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FAMILIA UNIVERSAL SCHOOL</t>
+          <t>CARLOS PAREJA PAZ SOLDAN</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.02645</t>
+          <t>331</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.02818</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>-12.03636</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.02362</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>320860</t>
+          <t>320841</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CARLOS PAREJA PAZ SOLDAN</t>
+          <t>LUCIE RYNNING DE ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.03636</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.02362</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>-12.0356</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-77.0264</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>695043</t>
+          <t>320822</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LAS MERCEDES DEL BOSQUE</t>
+          <t>3021 SAN JUAN MACIAS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.02053</t>
+          <t>548</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-77.03187</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>-12.0392</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-77.029</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>320822</t>
+          <t>320817</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>3021 SAN JUAN MACIAS</t>
+          <t>3019 PATRICIA TERESA RODRIGUEZ</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.0392</t>
+          <t>354</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-77.029</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>-12.02403</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-77.02494</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>321459</t>
+          <t>320799</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL PATROCINIO</t>
+          <t>3017 INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.0364</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-77.024733</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>-12.01641</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-77.03202</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>320638</t>
+          <t>320780</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2002 MARISCAL RAMON CASTILLA</t>
+          <t>3015 LOS ANGELES DE JESUS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.01641</t>
+          <t>884</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-77.03184</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>-12.023383</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-77.026933</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>321063</t>
+          <t>320761</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO</t>
+          <t>3012 JESUS DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.01822</t>
+          <t>338</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-77.02813</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>-12.02158</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-77.02685</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2619,22 +2619,22 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
           <t>-12.03648</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>-77.03897</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>321416</t>
+          <t>320723</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>INSTITUTO SEVILLA</t>
+          <t>3006 JOSE ERNESTO ECHENIQUE RODRIGUEZ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.03635</t>
+          <t>397</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-77.02566</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>-12.03736</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-77.015</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2743,22 +2743,22 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
           <t>-12.0367</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>-77.0268</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>606</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>320841</t>
+          <t>320681</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>LUCIE RYNNING DE ANTUNEZ DE MAYOLO</t>
+          <t>3001 ESTADOS UNIDOS MEXICANOS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.0356</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-77.0264</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>-12.03949</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-77.02807</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>320582</t>
+          <t>320676</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0392-3 SAN CRISTOBAL / 3003 SAN CRISTOBAL</t>
+          <t>2083 VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.03695</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-77.02269</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>-12.0307</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-77.0315</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>717078</t>
+          <t>320662</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - RIMAC SPORTING CRISTAL</t>
+          <t>2074 MARIA PARADO DE BELLIDO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.01977</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-77.03457</t>
+          <t>105</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>-12.029525</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-77.028075</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>321119</t>
+          <t>320657</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>BAUTISTA</t>
+          <t>2063 CORONEL JOSE FELIX BOGADO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.021983</t>
+          <t>964</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-77.030867</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>-12.01485</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-77.02612</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>533178</t>
+          <t>320643</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LAS MERCEDES DEL BOSQUE</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.025821</t>
+          <t>204</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-77.031486</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>-12.03823</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-77.01868</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>320780</t>
+          <t>320638</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>3015 LOS ANGELES DE JESUS</t>
+          <t>2002 MARISCAL RAMON CASTILLA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.023383</t>
+          <t>552</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-77.026933</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>-12.01641</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-77.03184</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>320676</t>
+          <t>320624</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2083 VIRGEN DEL CARMEN</t>
+          <t>NACIONAL RIMAC</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-12.0307</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-77.0315</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>-12.01898</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-77.03552</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>320799</t>
+          <t>320619</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>3017 INMACULADA CONCEPCION</t>
+          <t>RICARDO BENTIN</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.01641</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-77.03202</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>-12.0304</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-77.03694</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>320657</t>
+          <t>320582</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2063 CORONEL JOSE FELIX BOGADO</t>
+          <t>0392-3 SAN CRISTOBAL / 3003 SAN CRISTOBAL</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-12.01485</t>
+          <t>695</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-77.02612</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>-12.03695</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-77.02269</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>320624</t>
+          <t>320558</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>NACIONAL RIMAC</t>
+          <t>0391-2 SAN JUAN DE AMANCAES</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-12.01898</t>
+          <t>312</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-77.03552</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>-12.016</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-77.0268</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>320935</t>
+          <t>320501</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA CONSOLACION</t>
+          <t>0320</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.026783</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-77.031533</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>-12.016013</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-77.030832</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>320879</t>
+          <t>320488</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ESTHER CACERES SALGADO</t>
+          <t>049 NUESTRA SEÑORA DE GUADALUPE</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12.03029</t>
+          <t>359</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-77.03107</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>-12.03037</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-77.0315</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-RIMAC.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-RIMAC.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
